--- a/naver-place-crawler/results_health/사상구_PT.xlsx
+++ b/naver-place-crawler/results_health/사상구_PT.xlsx
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>대기구필라테스청담 주례점</t>
+          <t>뉴욕짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cjdeka1109@naver.com</t>
+          <t>cookieboy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>051-321-0304</t>
+          <t>0507-1323-5925</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로506번길 15 제일타워상가 2층</t>
+          <t>부산광역시 서구 대영로 34 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_UVxoxcb</t>
+          <t>https://www.instagram.com/newyork__gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>663</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
-        <v>176</v>
+        <v>265</v>
       </c>
       <c r="R2" t="n">
-        <v>839</v>
+        <v>296</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1489812277</t>
+          <t>1156765237</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489812277</t>
+          <t>https://m.place.naver.com/place/1156765237</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴욕짐 동대신점</t>
+          <t>더진짜휘트니스주례점 / 개인PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tjrwls1114@naver.com</t>
+          <t>the_realfitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1324-5925</t>
+          <t>051-314-5500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 서구 망양로 99 1, 2층</t>
+          <t>부산광역시 사상구 백양대로 370 5층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tjrwls1114</t>
+          <t>https://blog.naver.com/the_realfitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>15</v>
+        <v>191</v>
       </c>
       <c r="Q3" t="n">
-        <v>47</v>
+        <v>341</v>
       </c>
       <c r="R3" t="n">
-        <v>62</v>
+        <v>532</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,52 +730,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1983655996</t>
+          <t>1432337788</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983655996</t>
+          <t>https://m.place.naver.com/place/1432337788</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>합기도</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 엠케이짐</t>
+          <t>건아합기도</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lsw_gym@naver.com</t>
+          <t>dagymfit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1487-2777</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 삼덕로46번길 116 6층</t>
+          <t>부산광역시 사상구 백양대로 508 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/mk_gym</t>
+          <t>https://blog.naver.com/dagymfit</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -796,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,47 +824,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1083799054</t>
+          <t>13208389</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083799054</t>
+          <t>https://m.place.naver.com/place/13208389</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>체력단련,운동</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>두잇짐</t>
+          <t>빅터짐 헬스&amp;PT 주례점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>doit_pt@naver.com</t>
+          <t>victorgym01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1473-6464</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 냉정로 41 2층두잇짐</t>
+          <t>부산광역시 사상구 가야대로 256 가야 컴퓨터 상가 6, 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/doit_pt</t>
+          <t>https://blog.naver.com/victorgym01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>71</v>
+        <v>762</v>
       </c>
       <c r="Q5" t="n">
-        <v>170</v>
+        <v>451</v>
       </c>
       <c r="R5" t="n">
-        <v>241</v>
+        <v>1213</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1229534985</t>
+          <t>1650355008</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229534985</t>
+          <t>https://m.place.naver.com/place/1650355008</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -932,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>바로움PT</t>
+          <t>풀핏 덕포점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>baroum_pt@naver.com</t>
+          <t>gogogo4691-@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1353-2146</t>
+          <t>0507-1399-5081</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로 277 2층</t>
+          <t>부산광역시 사상구 사상로 336 2,3층 풀핏피트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/baroum_pt</t>
+          <t>http://pf.kakao.com/_xiGazX</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -969,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -980,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="Q6" t="n">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="R6" t="n">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,66 +1012,66 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2087182364</t>
+          <t>1081611995</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087182364</t>
+          <t>https://m.place.naver.com/place/1081611995</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뉴인핏 PT</t>
+          <t>피에스짐 학장점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>in-fit@naver.com</t>
+          <t>ps_gym_4@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1414-4020</t>
+          <t>0507-1463-5574</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 182 청호빌딩 3층</t>
+          <t>부산광역시 사상구 대동로 94 반도프라자 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/749373</t>
+          <t>https://open.kakao.com/o/sG35Kkkg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1074,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1083,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>268</v>
+        <v>408</v>
       </c>
       <c r="Q7" t="n">
-        <v>1987</v>
+        <v>586</v>
       </c>
       <c r="R7" t="n">
-        <v>2255</v>
+        <v>994</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38643118</t>
+          <t>1561426505</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38643118</t>
+          <t>https://m.place.naver.com/place/1561426505</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>올데이 그룹PT</t>
+          <t>감성피티 개금가야점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>yolo__j@naver.com</t>
+          <t>david8248@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1393-9684</t>
+          <t>0507-1311-7011</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 가야대로 472 보문빌딩 4층</t>
+          <t>부산광역시 부산진구 엄광로 67 2, 3, 4층 감성피티 개금가야점</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allday__gg</t>
+          <t>https://cafe.naver.com/gamsunggaya/80</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="Q8" t="n">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="R8" t="n">
-        <v>464</v>
+        <v>573</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1958976432</t>
+          <t>1480593913</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958976432</t>
+          <t>https://m.place.naver.com/place/1480593913</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아름스파</t>
+          <t>24시 헬스 피티 여성전용 솔휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>qkdxmrtn@naver.com</t>
+          <t>solfitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>051-991-0333</t>
+          <t>0507-1421-1052</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 304</t>
+          <t>부산광역시 사상구 사상로 230 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/qkdxmrtn</t>
+          <t>https://www.youtube.com/@solfitness_offical</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1267,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>564</v>
       </c>
       <c r="R9" t="n">
-        <v>156</v>
+        <v>712</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1092080195</t>
+          <t>36823614</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092080195</t>
+          <t>https://m.place.naver.com/place/36823614</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1316,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>이터널짐</t>
+          <t>블로썸핏 하단 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>applegustjrd@naver.com</t>
+          <t>blossomfit@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1333-2752</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 백양산로54번길 3 골든박스7층</t>
+          <t>부산광역시 사하구 낙동대로 491 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/applegustjrd</t>
+          <t>https://blog.naver.com/blossomfit</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Q10" t="n">
-        <v>334</v>
+        <v>1184</v>
       </c>
       <c r="R10" t="n">
-        <v>407</v>
+        <v>1349</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1043570317</t>
+          <t>1221239515</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043570317</t>
+          <t>https://m.place.naver.com/place/1221239515</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1402,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>개금워터캐슬사우나헬스/PT/GX</t>
+          <t>슈퍼짐 주례점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rormawater2004-@naver.com</t>
+          <t>wjdzm4956@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>051-891-5881</t>
+          <t>0507-1423-3427</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 냉정로178번길 21</t>
+          <t>부산광역시 사상구 백양대로 493 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/watergym_gg</t>
+          <t>https://www.instagram.com/super_gym_88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>205</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="R11" t="n">
-        <v>278</v>
+        <v>103</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>11821598</t>
+          <t>1913750950</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11821598</t>
+          <t>https://m.place.naver.com/place/1913750950</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1496,34 +1500,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오케이피트니스 구남점 헬스&amp;PT</t>
+          <t>404피트니스 헬스&amp;PT 덕포점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>okfitness-gunam@naver.com</t>
+          <t>404deokpo@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1473-0221</t>
+          <t>0507-1408-4044</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 북구 백양대로 1013 벽성빌딩 3층</t>
+          <t>부산광역시 사상구 사상로 303 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://litt.ly/okfitness_gunam</t>
+          <t>https://blog.naver.com/404deokpo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1533,7 +1537,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1553,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>421</v>
+        <v>67</v>
       </c>
       <c r="Q12" t="n">
-        <v>627</v>
+        <v>110</v>
       </c>
       <c r="R12" t="n">
-        <v>1048</v>
+        <v>177</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,66 +1572,66 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1579176380</t>
+          <t>2082509120</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579176380</t>
+          <t>https://m.place.naver.com/place/2082509120</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>뉴욕짐</t>
+          <t>오케이피트니스 주례점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ny_gym@naver.com</t>
+          <t>okfitness_jurye@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1323-5925</t>
+          <t>0507-1374-3985</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 서구 대영로 34 2층</t>
+          <t>부산광역시 사상구 백양대로 337 4, 5층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newyork__gym</t>
+          <t>https://www.okfitness.co.kr/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1638,7 +1642,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1647,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>31</v>
+        <v>299</v>
       </c>
       <c r="Q13" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="R13" t="n">
-        <v>296</v>
+        <v>576</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1156765237</t>
+          <t>1240563348</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156765237</t>
+          <t>https://m.place.naver.com/place/1240563348</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에프원피트니스 헬스&amp;PT 냉정점</t>
+          <t>헬스보이짐 하단점 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>f1nj0401@naver.com</t>
+          <t>healthboy34@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1440-2371</t>
+          <t>0507-1489-5775</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 374 6층, 7층</t>
+          <t>부산광역시 사하구 낙동남로 1403 2층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f1nj0401</t>
+          <t>https://blog.naver.com/healthboy34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>297</v>
+        <v>587</v>
       </c>
       <c r="Q14" t="n">
-        <v>430</v>
+        <v>632</v>
       </c>
       <c r="R14" t="n">
-        <v>727</v>
+        <v>1219</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,56 +1760,56 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1871691088</t>
+          <t>1791255308</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1871691088</t>
+          <t>https://m.place.naver.com/place/1791255308</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피에스짐 주례점 헬스 PT</t>
+          <t>대기구필라테스청담 모라점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ps_gym_4@naver.com</t>
+          <t>cjdeka0824@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1445-0954</t>
+          <t>0507-1462-8095</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로357번길 33 1층 피에스짐 주례점</t>
+          <t>부산광역시 사상구 백양대로 900 10층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ps_gym_4</t>
+          <t>https://pf.kakao.com/_eNwbG</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1815,7 +1819,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1826,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>613</v>
+        <v>649</v>
       </c>
       <c r="Q15" t="n">
-        <v>755</v>
+        <v>379</v>
       </c>
       <c r="R15" t="n">
-        <v>1368</v>
+        <v>1028</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,51 +1854,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1182425609</t>
+          <t>1239357620</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182425609</t>
+          <t>https://m.place.naver.com/place/1239357620</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>요가</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>럭키헬스장</t>
+          <t>바로움PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>luckygym7@naver.com</t>
+          <t>baroum_pt@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1320-3025</t>
+          <t>0507-1353-2146</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학장로 316 3층</t>
+          <t>부산광역시 사상구 학감대로 277 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/baroum_pt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,12 +1908,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1925,17 +1929,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2095755701</t>
+          <t>2087182364</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2095755701</t>
+          <t>https://m.place.naver.com/place/2087182364</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>냉정헬스장 썬짐</t>
+          <t>피트니스382 엄궁점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>always0519@naver.com</t>
+          <t>fitness382_eomgung@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>070-8117-1544</t>
+          <t>0507-1497-0436</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 주례로10번길 7 2층 3층</t>
+          <t>부산광역시 사상구 엄궁로 97 5층 피트니스382 엄궁점</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/always0519</t>
+          <t>https://blog.naver.com/fitness382_eomgung</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2019,17 +2023,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>262</v>
+        <v>147</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="R17" t="n">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,61 +2042,61 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1600151493</t>
+          <t>1261626295</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1600151493</t>
+          <t>https://m.place.naver.com/place/1261626295</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>개금 리부트핏 PT</t>
+          <t>필라걸 사상점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>reboot_fit@naver.com</t>
+          <t>pilasasang@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1357-9397</t>
+          <t>051-313-3232</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 냉정로 214 . 2층(개금동)</t>
+          <t>부산광역시 사상구 광장로81번길 30 8,9층 필라걸</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://m.blog.naver.com/reboot_fit</t>
+          <t>https://blog.naver.com/pilasasang</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2117,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Q18" t="n">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1668633780</t>
+          <t>1538621837</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1668633780</t>
+          <t>https://m.place.naver.com/place/1538621837</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2154,29 +2158,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>팰리스피트니스 헬스&amp;PT 1호점 모라</t>
+          <t>럭키헬스장</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>palace7979@naver.com</t>
+          <t>jyk5275@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1312-5736</t>
+          <t>0507-1320-3025</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 893 B1 (제일약국 / 참좋은 내과 / 뚜레쥬르 건물)</t>
+          <t>부산광역시 사상구 학장로 316 3층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/palacefitness_official/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2186,7 +2190,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2207,17 +2211,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>783</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2226,51 +2230,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1942470035</t>
+          <t>2095755701</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942470035</t>
+          <t>https://m.place.naver.com/place/2095755701</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>트렌드핏 PT 사상점</t>
+          <t>퍼스널짐</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>trendfit_hmmy@naver.com</t>
+          <t>personal___gym@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1388-1578</t>
+          <t>0507-1474-0802</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 200 엠시티빌딩 13층</t>
+          <t>부산광역시 서구 대영로85번길 14 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/trendfit_hmmy</t>
+          <t>http://http//xn--p50b964aohf5wk.com/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2285,7 +2289,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2305,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>274</v>
+        <v>47</v>
       </c>
       <c r="Q20" t="n">
-        <v>735</v>
+        <v>58</v>
       </c>
       <c r="R20" t="n">
-        <v>1009</v>
+        <v>105</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,51 +2324,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1041650796</t>
+          <t>1596917839</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1041650796</t>
+          <t>https://m.place.naver.com/place/1596917839</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>헬스&amp;PT 인핏 덕천점</t>
+          <t>404피트니스 헬스&amp;PT 하단점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>infit_gym@naver.com</t>
+          <t>404fitnesshadan@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1374-5020</t>
+          <t>0507-1395-4026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 북구 기찰로 3 유니다로얄 상가건물 4층</t>
+          <t>부산광역시 사하구 낙동대로 487 4층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/infit_gym</t>
+          <t>https://www.instagram.com/404_fitness_hadan/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2390,7 +2394,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2399,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="Q21" t="n">
-        <v>1784</v>
+        <v>289</v>
       </c>
       <c r="R21" t="n">
-        <v>2182</v>
+        <v>708</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2414,47 +2418,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1054512325</t>
+          <t>1669341529</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054512325</t>
+          <t>https://m.place.naver.com/place/1669341529</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>래빗짐 냉정점</t>
+          <t>바롬트레이닝센터</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dearnahee@naver.com</t>
+          <t>baromtraining@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1371-9777</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 370 지하1층</t>
+          <t>부산광역시 서구 대영로 17 6층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rabbit.gym/</t>
+          <t>https://blog.naver.com/baromtraining</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2469,7 +2477,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2480,7 +2488,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2489,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>161</v>
+        <v>42</v>
       </c>
       <c r="Q22" t="n">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="R22" t="n">
-        <v>461</v>
+        <v>250</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,66 +2512,66 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1150547590</t>
+          <t>1409428552</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1150547590</t>
+          <t>https://m.place.naver.com/place/1409428552</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>오케이피트니스 주례점 헬스&amp;PT</t>
+          <t>바론 필라테스 &amp; PT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>okfitness_jurye@naver.com</t>
+          <t>barongym@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1374-3985</t>
+          <t>0507-1421-9877</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 337 4, 5층</t>
+          <t>부산광역시 사상구 엄궁로 91 바론 필라테스&amp; PT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.okfitness.co.kr/</t>
+          <t>https://www.instagram.com/baron.pilates.pt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2574,7 +2582,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>299</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>273</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>572</v>
+        <v>6</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1240563348</t>
+          <t>1854988973</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240563348</t>
+          <t>https://m.place.naver.com/place/1854988973</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2620,39 +2628,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>헬스보이짐 하단점 PT&amp;헬스</t>
+          <t>오케이피트니스 개금점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>healthboy34@naver.com</t>
+          <t>okfitness19@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1489-5775</t>
+          <t>0507-1403-9791</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동남로 1403 2층</t>
+          <t>부산광역시 부산진구 개금온정로 5 201호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy34</t>
+          <t>https://okfitness.co.kr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2668,7 +2676,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2677,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>586</v>
+        <v>271</v>
       </c>
       <c r="Q24" t="n">
-        <v>629</v>
+        <v>208</v>
       </c>
       <c r="R24" t="n">
-        <v>1215</v>
+        <v>479</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,51 +2700,51 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1791255308</t>
+          <t>2001258467</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791255308</t>
+          <t>https://m.place.naver.com/place/2001258467</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>바디로운필라테스 덕천점</t>
+          <t>에프원피트니스 헬스&amp;PT 냉정점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bodyroun02@naver.com</t>
+          <t>f1nj0401@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1451-1026</t>
+          <t>0507-1440-2371</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 북구 만덕대로27번길 3 세빈빌딩 8층 바디로운 필라테스</t>
+          <t>부산광역시 사상구 가야대로 374 6층, 7층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyroun02</t>
+          <t>https://blog.naver.com/f1nj0401</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2771,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>508</v>
+        <v>300</v>
       </c>
       <c r="Q25" t="n">
-        <v>162</v>
+        <v>433</v>
       </c>
       <c r="R25" t="n">
-        <v>670</v>
+        <v>733</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1970826874</t>
+          <t>1871691088</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1970826874</t>
+          <t>https://m.place.naver.com/place/1871691088</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2816,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>피티데이</t>
+          <t>핏튜브짐 &amp; 필라테스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pt_day@naver.com</t>
+          <t>boong_see@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1432-8856</t>
+          <t>0507-1465-5152</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 가야대로 480-1 4층 피티데이</t>
+          <t>부산광역시 사하구 하신번영로 417 2층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pt_day</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2840,12 +2848,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2861,17 +2869,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="R26" t="n">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,51 +2888,51 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1068613419</t>
+          <t>1226166767</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1068613419</t>
+          <t>https://m.place.naver.com/place/1226166767</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>이젠퍼스널트레이닝</t>
+          <t>올아웃 휘트니스 PT 사상점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ezenstudio@naver.com</t>
+          <t>kindlydevil@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1420-3406</t>
+          <t>0507-1398-7759</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 서구 구덕로322번길 7 6층</t>
+          <t>부산광역시 사상구 운산로 48 4층 올아웃 휘트니스</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ezenstudio</t>
+          <t>https://blog.naver.com/kindlydevil</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2959,13 +2967,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="Q27" t="n">
-        <v>49</v>
+        <v>599</v>
       </c>
       <c r="R27" t="n">
-        <v>81</v>
+        <v>647</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1274402269</t>
+          <t>1564802494</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1274402269</t>
+          <t>https://m.place.naver.com/place/1564802494</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2996,29 +3004,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>피트니스382 엄궁점</t>
+          <t>트렌드핏 PT 사상점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>fitness382_eomgung@naver.com</t>
+          <t>trendfit_hmmy@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1497-0436</t>
+          <t>0507-1388-1578</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 97 5층 피트니스382 엄궁점</t>
+          <t>부산광역시 사상구 사상로 200 엠시티빌딩 13층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness382_eomgung</t>
+          <t>https://blog.naver.com/trendfit_hmmy</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3053,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>147</v>
+        <v>273</v>
       </c>
       <c r="Q28" t="n">
-        <v>91</v>
+        <v>734</v>
       </c>
       <c r="R28" t="n">
-        <v>238</v>
+        <v>1007</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1261626295</t>
+          <t>1041650796</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261626295</t>
+          <t>https://m.place.naver.com/place/1041650796</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3090,29 +3098,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>더진짜휘트니스주례점 / 개인PT</t>
+          <t>알통클럽 휘트니스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>the_realfitness@naver.com</t>
+          <t>daeilband007@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>051-314-5500</t>
+          <t>051-317-2999</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 370 5층</t>
+          <t>부산광역시 사상구 낙동대로 751 동일메가타워 7층 알통클럽휘트니스</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/the_realfitness</t>
+          <t>https://blog.naver.com/daeilband007</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3147,13 +3155,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="Q29" t="n">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="R29" t="n">
-        <v>527</v>
+        <v>460</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3170,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1432337788</t>
+          <t>35769362</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1432337788</t>
+          <t>https://m.place.naver.com/place/35769362</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3184,29 +3192,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>하단pt 더원짐</t>
+          <t>이젠퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jlove518@naver.com</t>
+          <t>ezenstudio@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1411-0656</t>
+          <t>0507-1420-3406</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 381-4 2층 더원짐</t>
+          <t>부산광역시 서구 구덕로322번길 7 6층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jlove518</t>
+          <t>https://blog.naver.com/ezenstudio</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3232,7 +3240,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3241,13 +3249,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="Q30" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="R30" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,47 +3264,51 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>53386360</t>
+          <t>1274402269</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/53386360</t>
+          <t>https://m.place.naver.com/place/1274402269</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>블로썸핏 하단 PT</t>
+          <t>냉정헬스장 썬짐</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>blossomfit@naver.com</t>
+          <t>always0519@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>070-8117-1544</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 491 7층</t>
+          <t>부산광역시 사상구 주례로10번길 7 2층 3층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blossomfit</t>
+          <t>https://blog.naver.com/always0519</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3327,17 +3339,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>164</v>
+        <v>262</v>
       </c>
       <c r="Q31" t="n">
-        <v>1180</v>
+        <v>13</v>
       </c>
       <c r="R31" t="n">
-        <v>1344</v>
+        <v>275</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3358,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1221239515</t>
+          <t>1600151493</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221239515</t>
+          <t>https://m.place.naver.com/place/1600151493</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3368,29 +3380,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>에이치포스포츠</t>
+          <t>래빗짐 냉정점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>atbud008@naver.com</t>
+          <t>dearnahee@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>051-715-0705</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 945 3층</t>
+          <t>부산광역시 사상구 가야대로 370 지하1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/atbud008</t>
+          <t>https://www.instagram.com/rabbit.gym/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3405,7 +3413,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3416,22 +3424,22 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>299</v>
       </c>
       <c r="R32" t="n">
-        <v>31</v>
+        <v>458</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,51 +3448,51 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>465072208</t>
+          <t>1150547590</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/465072208</t>
+          <t>https://m.place.naver.com/place/1150547590</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>풀핏 덕포점</t>
+          <t>라인피트니스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gogogo4691-@naver.com</t>
+          <t>lineptshop@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1399-5081</t>
+          <t>0507-1373-3165</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 336 2,3층 풀핏피트니스</t>
+          <t>부산광역시 사상구 대동로 129 육오빌딩(학장동물병원 건물)4층 라인피트니스</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gogogo4691-</t>
+          <t>https://www.instagram.com/sehwan_linept/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3499,7 +3507,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3519,13 +3527,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="Q33" t="n">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="R33" t="n">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3542,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1081611995</t>
+          <t>1006677354</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081611995</t>
+          <t>https://m.place.naver.com/place/1006677354</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3556,29 +3564,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>라인피트니스</t>
+          <t>불독짐 학장점 해머스트렝스오피셜&amp;요가필라테스&amp;줌바&amp;GX</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lineptshop@naver.com</t>
+          <t>bulldoggym_hakjang@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1373-3165</t>
+          <t>0507-1407-8857</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 129 육오빌딩(학장동물병원 건물)4층 라인피트니스</t>
+          <t>부산광역시 사상구 학감대로 117 5층 불독짐</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sehwan_linept/</t>
+          <t>https://open.kakao.com/o/scxu9x0h</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3604,7 +3612,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3613,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>163</v>
+        <v>329</v>
       </c>
       <c r="Q34" t="n">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="R34" t="n">
-        <v>342</v>
+        <v>601</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3636,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1006677354</t>
+          <t>38282308</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006677354</t>
+          <t>https://m.place.naver.com/place/38282308</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3650,34 +3658,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에프원피트니스 헬스&amp;PT 사상점</t>
+          <t>KN피트니스 주례점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>f1sasang@naver.com</t>
+          <t>tgloveheyyo@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1362-1513</t>
+          <t>0507-1307-0912</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 208-1 TOP 빌딩 13층</t>
+          <t>부산광역시 사상구 가야대로 365 2,3층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f1sasang</t>
+          <t>https://pf.kakao.com/_WxkCtu</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3687,7 +3695,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3698,7 +3706,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3707,13 +3715,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>617</v>
+        <v>114</v>
       </c>
       <c r="Q35" t="n">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="R35" t="n">
-        <v>734</v>
+        <v>319</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3730,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1557069608</t>
+          <t>36395479</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1557069608</t>
+          <t>https://m.place.naver.com/place/36395479</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3744,29 +3752,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>동아기능성운동트레이닝센터</t>
+          <t>하단pt 더원짐</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dfet0226@naver.com</t>
+          <t>jlove518@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1494-7910</t>
+          <t>0507-1411-0656</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로550번길 37 예술체육대학1관 106호</t>
+          <t>부산광역시 사하구 하신번영로 381-4 2층 더원짐</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dfet0226</t>
+          <t>https://blog.naver.com/jlove518</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3792,7 +3800,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3801,13 +3809,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="Q36" t="n">
-        <v>297</v>
+        <v>120</v>
       </c>
       <c r="R36" t="n">
-        <v>458</v>
+        <v>189</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,66 +3824,66 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1619665911</t>
+          <t>53386360</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1619665911</t>
+          <t>https://m.place.naver.com/place/53386360</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>메디제이필라테스 사상점</t>
+          <t>헬스&amp;PT 인핏 덕천점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kikunid1@naver.com</t>
+          <t>infit_gym@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1408-3404</t>
+          <t>0507-1374-5020</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 7 르네시떼 홈플러스 B1 메디제이필라테스 사상점</t>
+          <t>부산광역시 북구 기찰로 3 유니다로얄 상가건물 4층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/780007</t>
+          <t>https://blog.naver.com/infit_gym</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3886,7 +3894,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3895,13 +3903,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>32</v>
+        <v>401</v>
       </c>
       <c r="Q37" t="n">
-        <v>514</v>
+        <v>1787</v>
       </c>
       <c r="R37" t="n">
-        <v>546</v>
+        <v>2188</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +3918,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1641385781</t>
+          <t>1054512325</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1641385781</t>
+          <t>https://m.place.naver.com/place/1054512325</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3932,39 +3940,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오케이피트니스 개금점 헬스&amp;PT</t>
+          <t>피크짐 학장점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>okfitness19@naver.com</t>
+          <t>peakgym2@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1403-9791</t>
+          <t>0507-1341-7526</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 개금온정로 5 201호</t>
+          <t>부산광역시 사상구 대동로 140 피크짐 학장점</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://okfitness.co.kr</t>
+          <t>https://blog.naver.com/peakgym2</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3980,7 +3988,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3989,13 +3997,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>258</v>
+        <v>857</v>
       </c>
       <c r="Q38" t="n">
-        <v>200</v>
+        <v>847</v>
       </c>
       <c r="R38" t="n">
-        <v>458</v>
+        <v>1704</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,17 +4012,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2001258467</t>
+          <t>1649867638</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001258467</t>
+          <t>https://m.place.naver.com/place/1649867638</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4026,29 +4034,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>피크짐 학장점</t>
+          <t>아름스파</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>peakgym2@naver.com</t>
+          <t>qkdxmrtn@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1341-7526</t>
+          <t>051-991-0333</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 140 피크짐 학장점</t>
+          <t>부산광역시 사상구 대동로 304</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/peakgym2</t>
+          <t>https://blog.naver.com/qkdxmrtn</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4079,17 +4087,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>850</v>
+        <v>144</v>
       </c>
       <c r="Q39" t="n">
-        <v>842</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>1692</v>
+        <v>156</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4098,51 +4106,51 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1649867638</t>
+          <t>1092080195</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1649867638</t>
+          <t>https://m.place.naver.com/place/1092080195</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>24시 헬스 피티 여성전용 솔휘트니스</t>
+          <t>풀핏 구남점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>solfitness@naver.com</t>
+          <t>cjfxoddl123@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1421-1052</t>
+          <t>0507-1376-9869</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 230 3층</t>
+          <t>부산광역시 북구 백양대로 1028 5층 501호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@solfitness_offical</t>
+          <t>http://pf.kakao.com/_FgJzX</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4168,7 +4176,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4177,13 +4185,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="Q40" t="n">
-        <v>563</v>
+        <v>112</v>
       </c>
       <c r="R40" t="n">
-        <v>711</v>
+        <v>203</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4192,17 +4200,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>36823614</t>
+          <t>2073542672</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36823614</t>
+          <t>https://m.place.naver.com/place/2073542672</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4214,34 +4222,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KN피트니스 주례점</t>
+          <t>엘리먼트 휘트니스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tgloveheyyo@naver.com</t>
+          <t>kycbyc@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1307-0912</t>
+          <t>051-304-2255</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 365 2,3층</t>
+          <t>부산광역시 사상구 백양대로 987 스파캐슬 7층 엘리먼트 휘트니스</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_WxkCtu</t>
+          <t>https://www.instagram.com/element_fitness987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4262,7 +4270,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4271,13 +4279,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="Q41" t="n">
-        <v>205</v>
+        <v>86</v>
       </c>
       <c r="R41" t="n">
-        <v>318</v>
+        <v>122</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4286,56 +4294,56 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>36395479</t>
+          <t>11878707</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36395479</t>
+          <t>https://m.place.naver.com/place/11878707</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>트랜스바디짐 학장점</t>
+          <t>이터널짐</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>transbody02@naver.com</t>
+          <t>applegustjrd@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1364-9625</t>
+          <t>0507-1333-2752</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로123번길 68 AK 빌딩 삼정그린코아 맞은편</t>
+          <t>부산광역시 부산진구 백양산로54번길 3 골든박스7층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://youtube.com/@트랜스바디짐학장점</t>
+          <t>https://blog.naver.com/applegustjrd</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4345,7 +4353,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4365,13 +4373,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="Q42" t="n">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="R42" t="n">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,56 +4388,56 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>37335417</t>
+          <t>1043570317</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37335417</t>
+          <t>https://m.place.naver.com/place/1043570317</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;PT 학장점</t>
+          <t>피티데이</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>404fitness_hakjang@naver.com</t>
+          <t>pt_day@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1390-4024</t>
+          <t>0507-1432-8856</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 123 4층</t>
+          <t>부산광역시 부산진구 가야대로 480-1 4층 피티데이</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/404_fitness_hakjang?igsh=emR4aTI2Y3p0NzNu</t>
+          <t>https://blog.naver.com/pt_day</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4459,13 +4467,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>795</v>
+        <v>36</v>
       </c>
       <c r="Q43" t="n">
-        <v>525</v>
+        <v>68</v>
       </c>
       <c r="R43" t="n">
-        <v>1320</v>
+        <v>104</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,51 +4482,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1215321048</t>
+          <t>1068613419</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1215321048</t>
+          <t>https://m.place.naver.com/place/1068613419</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>퍼스널짐</t>
+          <t>미라클짐 헬스&amp;PT 필라테스 학장점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>personal___gym@naver.com</t>
+          <t>miraclegym2@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1474-0802</t>
+          <t>051-313-7705</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 서구 대영로85번길 14 3층</t>
+          <t>부산광역시 사상구 대동로 95 3층 미라클짐 학장점</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://http//xn--p50b964aohf5wk.com/</t>
+          <t>https://www.instagram.com/miracle__gym?igsh=YXp2czJxNmdiMjA0&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4553,13 +4561,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="Q44" t="n">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="R44" t="n">
-        <v>105</v>
+        <v>266</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4568,17 +4576,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1596917839</t>
+          <t>1169221564</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596917839</t>
+          <t>https://m.place.naver.com/place/1169221564</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4590,34 +4598,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>불독짐 학장점 해머스트렝스오피셜&amp;요가필라테스&amp;줌바&amp;GX</t>
+          <t>헬스버디짐&amp;스피닝&amp;줌바&amp;요가&amp;필라테스 사상점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bulldoggym_hakjang@naver.com</t>
+          <t>healthbuddy_sasang@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1407-8857</t>
+          <t>0507-1466-0195</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 학감대로 117 5층 불독짐</t>
+          <t>부산광역시 사상구 운산로 43 3,4층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/scxu9x0h</t>
+          <t>https://www.instagram.com/healthbuddygym_sasang</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4638,7 +4646,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4647,13 +4655,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>327</v>
+        <v>1319</v>
       </c>
       <c r="Q45" t="n">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="R45" t="n">
-        <v>596</v>
+        <v>1625</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4662,51 +4670,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>38282308</t>
+          <t>1858671457</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38282308</t>
+          <t>https://m.place.naver.com/place/1858671457</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>엔제이피트니스 냉정점 헬스&amp;PT&amp;GX</t>
+          <t>필라테스제시카PT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>njfitness@naver.com</t>
+          <t>bellyhy@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>051-913-4522</t>
+          <t>0507-1337-1689</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 384 7층 702호</t>
+          <t>부산광역시 사상구 백양대로 493 양지아카데미텔 3층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/njfitness</t>
+          <t>https://blog.naver.com/bellyhy</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4741,13 +4749,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1269</v>
+        <v>44</v>
       </c>
       <c r="Q46" t="n">
-        <v>563</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>1832</v>
+        <v>59</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,51 +4764,51 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1138994000</t>
+          <t>1069045430</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138994000</t>
+          <t>https://m.place.naver.com/place/1069045430</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>필라테스제시카PT</t>
+          <t>몽키짐 개금점,가야점,동의대점 1호점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bellyhy@naver.com</t>
+          <t>jevelyy@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1337-1689</t>
+          <t>051-892-2906</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 493 양지아카데미텔 3층</t>
+          <t>부산광역시 부산진구 냉정로 265 보광맨션 상가 B1층 몽키짐</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bellyhy</t>
+          <t>https://blog.naver.com/jevelyy</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4835,13 +4843,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="R47" t="n">
-        <v>58</v>
+        <v>130</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4850,17 +4858,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1069045430</t>
+          <t>1834519415</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1069045430</t>
+          <t>https://m.place.naver.com/place/1834519415</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4872,34 +4880,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>피에스짐 학장점 헬스 PT</t>
+          <t>개금워터캐슬사우나헬스/PT/GX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ps_gym_4@naver.com</t>
+          <t>rormawater2004-@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1463-5574</t>
+          <t>051-891-5881</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 94 반도프라자 4층</t>
+          <t>부산광역시 부산진구 냉정로178번길 21</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sG35Kkkg</t>
+          <t>https://www.instagram.com/watergym_gg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4920,7 +4928,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4929,13 +4937,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>403</v>
+        <v>205</v>
       </c>
       <c r="Q48" t="n">
-        <v>581</v>
+        <v>73</v>
       </c>
       <c r="R48" t="n">
-        <v>984</v>
+        <v>278</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4944,17 +4952,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1561426505</t>
+          <t>11821598</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1561426505</t>
+          <t>https://m.place.naver.com/place/11821598</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4966,29 +4974,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>담덕엄궁헬스</t>
+          <t>워너짐 헬스&amp;PT 하단점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>alivel12@naver.com</t>
+          <t>wannagym87@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1429-5975</t>
+          <t>0507-1477-1511</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 204 2층</t>
+          <t>부산광역시 사하구 하신번영로 352 우리마트 2층(하단동)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/alivel12</t>
+          <t>https://www.instagram.com/wannagym11_hadan</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5003,7 +5011,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5019,17 +5027,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>58</v>
+        <v>399</v>
       </c>
       <c r="Q49" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="R49" t="n">
-        <v>148</v>
+        <v>450</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5038,17 +5046,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1213885647</t>
+          <t>1180864218</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1213885647</t>
+          <t>https://m.place.naver.com/place/1180864218</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5060,29 +5068,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>매료피티</t>
+          <t>비앤비짐 PT 개금점,가야점,동의대점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>no1jin2@naver.com</t>
+          <t>happy_jsy_@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1396-4885</t>
+          <t>0507-1315-8491</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 승학로 19 4층</t>
+          <t>부산광역시 부산진구 가야대로 521 3층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/maeryo_official777</t>
+          <t>https://blog.naver.com/happy_jsy_</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5097,7 +5105,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5117,13 +5125,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="Q50" t="n">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="R50" t="n">
-        <v>410</v>
+        <v>178</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5132,51 +5140,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1438184043</t>
+          <t>1480246578</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1438184043</t>
+          <t>https://m.place.naver.com/place/1480246578</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>바론 필라테스 &amp; PT</t>
+          <t>엔제이피트니스 냉정점 헬스&amp;PT&amp;GX</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>barongym@naver.com</t>
+          <t>njfitness@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1421-9877</t>
+          <t>051-913-4522</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 엄궁로 91 바론 필라테스&amp; PT</t>
+          <t>부산광역시 사상구 가야대로 384 7층 702호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/baron.pilates.pt</t>
+          <t>https://blog.naver.com/njfitness</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5191,7 +5199,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5211,13 +5219,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>1287</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>556</v>
       </c>
       <c r="R51" t="n">
-        <v>6</v>
+        <v>1843</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5226,17 +5234,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1854988973</t>
+          <t>1138994000</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1854988973</t>
+          <t>https://m.place.naver.com/place/1138994000</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5248,29 +5256,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>비앤비짐 PT 개금점,가야점,동의대점</t>
+          <t>뉴욕짐 동대신점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>happy_jsy_@naver.com</t>
+          <t>tjrwls1114@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1315-8491</t>
+          <t>0507-1324-5925</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 가야대로 521 3층</t>
+          <t>부산광역시 서구 망양로 99 1, 2층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/happy_jsy_</t>
+          <t>https://blog.naver.com/tjrwls1114</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5305,13 +5313,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="Q52" t="n">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="R52" t="n">
-        <v>178</v>
+        <v>62</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5320,61 +5328,61 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1480246578</t>
+          <t>1983655996</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1480246578</t>
+          <t>https://m.place.naver.com/place/1983655996</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에프원 피트니스 헬스&amp;PT 모라점</t>
+          <t>메디제이필라테스 사상점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mora44@naver.com</t>
+          <t>kikunid1@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1328-1146</t>
+          <t>0507-1408-3404</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 524 8층 801호</t>
+          <t>부산광역시 사상구 광장로 7 르네시떼 홈플러스 B1 메디제이필라테스 사상점</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f1fitness_moraboss/</t>
+          <t>https://booking.naver.com/booking/12/bizes/780007</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5390,7 +5398,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5399,13 +5407,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>272</v>
+        <v>33</v>
       </c>
       <c r="Q53" t="n">
-        <v>54</v>
+        <v>518</v>
       </c>
       <c r="R53" t="n">
-        <v>326</v>
+        <v>551</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5414,51 +5422,51 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1178892172</t>
+          <t>1641385781</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1178892172</t>
+          <t>https://m.place.naver.com/place/1641385781</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>풀핏 구남점</t>
+          <t>에프원피트니스 헬스&amp;PT 사상점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>cjfxoddl123@naver.com</t>
+          <t>f1sasang@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1376-9869</t>
+          <t>0507-1362-1513</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 북구 백양대로 1028 5층 501호</t>
+          <t>부산광역시 사상구 사상로 208-1 TOP 빌딩 13층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cjfxoddl123</t>
+          <t>https://blog.naver.com/f1sasang</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5493,13 +5501,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="Q54" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="R54" t="n">
-        <v>201</v>
+        <v>739</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5508,17 +5516,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2073542672</t>
+          <t>1557069608</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2073542672</t>
+          <t>https://m.place.naver.com/place/1557069608</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5530,29 +5538,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;PT 덕포점</t>
+          <t>담덕엄궁헬스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>404deokpo@naver.com</t>
+          <t>alivel12@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1408-4044</t>
+          <t>0507-1429-5975</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 303 3층</t>
+          <t>부산광역시 사상구 엄궁로 204 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/404deokpo</t>
+          <t>https://blog.naver.com/alivel12</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5583,17 +5591,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q55" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="R55" t="n">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5602,56 +5610,52 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>2082509120</t>
+          <t>1213885647</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082509120</t>
+          <t>https://m.place.naver.com/place/1213885647</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>미라클짐24H&amp;기구필라테스</t>
+          <t>헬스&amp;PT 엠케이짐</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>miraclegym2@naver.com</t>
+          <t>lsw_gym@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>051-313-7705</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 대동로 95 3층 미라클짐 학장점</t>
+          <t>부산광역시 사상구 삼덕로46번길 116 6층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miracle__gym?igsh=YXp2czJxNmdiMjA0&amp;utm_source=qr</t>
+          <t>https://link.inpock.co.kr/mk_gym</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5661,7 +5665,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5681,13 +5685,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="Q56" t="n">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="R56" t="n">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5696,56 +5700,56 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1169221564</t>
+          <t>1083799054</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1169221564</t>
+          <t>https://m.place.naver.com/place/1083799054</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>감성피티 개금가야점</t>
+          <t>트랜스바디짐 주례점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>david8248@naver.com</t>
+          <t>pysook53@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1311-7011</t>
+          <t>0507-1407-6891</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 엄광로 67 2, 3, 4층 감성피티 개금가야점</t>
+          <t>부산광역시 사상구 백양대로 372-16 주례반도보라상가 4층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/gamsunggaya/80</t>
+          <t>https://blog.naver.com/pysook53</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5755,7 +5759,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5775,13 +5779,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>219</v>
+        <v>11</v>
       </c>
       <c r="Q57" t="n">
-        <v>351</v>
+        <v>253</v>
       </c>
       <c r="R57" t="n">
-        <v>570</v>
+        <v>264</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5790,56 +5794,56 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1480593913</t>
+          <t>33085242</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1480593913</t>
+          <t>https://m.place.naver.com/place/33085242</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>대기구필라테스청담 모라점</t>
+          <t>에프원 피트니스 헬스&amp;PT 모라점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>cjdeka0824@naver.com</t>
+          <t>mora44@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1462-8095</t>
+          <t>0507-1328-1146</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 900 10층</t>
+          <t>부산광역시 사상구 사상로 524 8층 801호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_eNwbG</t>
+          <t>https://www.instagram.com/f1fitness_moraboss/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5860,7 +5864,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5869,13 +5873,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>643</v>
+        <v>303</v>
       </c>
       <c r="Q58" t="n">
-        <v>376</v>
+        <v>55</v>
       </c>
       <c r="R58" t="n">
-        <v>1019</v>
+        <v>358</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5884,51 +5888,51 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1239357620</t>
+          <t>1178892172</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1239357620</t>
+          <t>https://m.place.naver.com/place/1178892172</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>더인핏PT&amp;헬스</t>
+          <t>바디메틱 PT센터</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>the-infit@naver.com</t>
+          <t>bodymetic_pt@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1340-3051</t>
+          <t>0507-1379-9309</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 사상로 201 애플아울렛 별관 B동 4층</t>
+          <t>부산광역시 사상구 백양대로 905-1 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/the-infit</t>
+          <t>https://open.kakao.com/o/sB45901c</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5943,7 +5947,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5954,7 +5958,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5963,13 +5967,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>922</v>
+        <v>37</v>
       </c>
       <c r="Q59" t="n">
-        <v>589</v>
+        <v>54</v>
       </c>
       <c r="R59" t="n">
-        <v>1511</v>
+        <v>91</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5978,17 +5982,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1307555029</t>
+          <t>1773103620</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1307555029</t>
+          <t>https://m.place.naver.com/place/1773103620</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6000,44 +6004,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>슈퍼짐 주례점</t>
+          <t>오케이피트니스 대신점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>wjdzm4956@naver.com</t>
+          <t>okfitness-daeshin@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1423-3427</t>
+          <t>0507-1448-1476</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 493 401호</t>
+          <t>부산광역시 서구 구덕로 317-1 홈플러스익스프레스 4층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/super_gym_88</t>
+          <t>https://www.okfitness.co.kr/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6048,7 +6052,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6057,13 +6061,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>18</v>
+        <v>451</v>
       </c>
       <c r="Q60" t="n">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="R60" t="n">
-        <v>103</v>
+        <v>693</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6072,51 +6076,51 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1913750950</t>
+          <t>1506395945</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913750950</t>
+          <t>https://m.place.naver.com/place/1506395945</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>바디메틱 PT센터</t>
+          <t>대기구필라테스청담 주례점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jerome2681@naver.com</t>
+          <t>cjdeka1109@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1379-9309</t>
+          <t>051-321-0304</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 905-1 2층</t>
+          <t>부산광역시 사상구 백양대로506번길 15 제일타워상가 2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sB45901c</t>
+          <t>http://pf.kakao.com/_UVxoxcb</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6151,13 +6155,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>37</v>
+        <v>666</v>
       </c>
       <c r="Q61" t="n">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="R61" t="n">
-        <v>91</v>
+        <v>847</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6166,51 +6170,51 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1773103620</t>
+          <t>1489812277</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1773103620</t>
+          <t>https://m.place.naver.com/place/1489812277</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>올아웃 휘트니스 PT 사상점</t>
+          <t>404피트니스 헬스&amp;pt 사상점</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kindlydevil@naver.com</t>
+          <t>404sasang_@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1398-7759</t>
+          <t>0507-1309-4044</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 운산로 48 4층 올아웃 휘트니스</t>
+          <t>부산광역시 사상구 광장로 84 하이앤드 4, 5층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kindlydevil</t>
+          <t>https://blog.naver.com/404sasang_</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6245,13 +6249,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>48</v>
+        <v>593</v>
       </c>
       <c r="Q62" t="n">
-        <v>594</v>
+        <v>682</v>
       </c>
       <c r="R62" t="n">
-        <v>642</v>
+        <v>1275</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6260,17 +6264,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1564802494</t>
+          <t>1720813988</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564802494</t>
+          <t>https://m.place.naver.com/place/1720813988</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6282,29 +6286,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>오성피트니스 대신점</t>
+          <t>매료피티</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>momjjang_@naver.com</t>
+          <t>no1jin2@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1439-5553</t>
+          <t>0507-1396-4885</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 서구 보수대로 198-1 1, 2층 오성피트니스</t>
+          <t>부산광역시 사하구 승학로 19 4층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/momjjang_</t>
+          <t>https://www.instagram.com/maeryo_official777</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6319,7 +6323,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6339,13 +6343,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="Q63" t="n">
-        <v>487</v>
+        <v>300</v>
       </c>
       <c r="R63" t="n">
-        <v>628</v>
+        <v>408</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6354,51 +6358,51 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1944190273</t>
+          <t>1438184043</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944190273</t>
+          <t>https://m.place.naver.com/place/1438184043</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>몽키짐 개금점,가야점,동의대점 1호점</t>
+          <t>404피트니스 헬스&amp;PT 학장점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jevelyy@naver.com</t>
+          <t>404fitness_hakjang@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>051-892-2906</t>
+          <t>0507-1390-4024</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 냉정로 265 보광맨션 상가 B1층 몽키짐</t>
+          <t>부산광역시 사상구 대동로 123 4층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jevelyy</t>
+          <t>https://www.instagram.com/404_fitness_hakjang?igsh=emR4aTI2Y3p0NzNu</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6413,7 +6417,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6433,13 +6437,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>30</v>
+        <v>801</v>
       </c>
       <c r="Q64" t="n">
-        <v>100</v>
+        <v>537</v>
       </c>
       <c r="R64" t="n">
-        <v>130</v>
+        <v>1338</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6448,51 +6452,47 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1834519415</t>
+          <t>1215321048</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1834519415</t>
+          <t>https://m.place.naver.com/place/1215321048</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>체력단련,운동</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>빅터짐 헬스&amp;PT 주례점</t>
+          <t>두잇짐</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>victorgym01@naver.com</t>
+          <t>doit_pt@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1473-6464</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 가야대로 256 가야 컴퓨터 상가 6, 7층</t>
+          <t>부산광역시 사상구 냉정로 41 2층두잇짐</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/victorgym01</t>
+          <t>https://blog.naver.com/doit_pt</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6527,13 +6527,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>762</v>
+        <v>74</v>
       </c>
       <c r="Q65" t="n">
-        <v>447</v>
+        <v>172</v>
       </c>
       <c r="R65" t="n">
-        <v>1209</v>
+        <v>246</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6542,17 +6542,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1650355008</t>
+          <t>1229534985</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650355008</t>
+          <t>https://m.place.naver.com/place/1229534985</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6564,29 +6564,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>뉴핏 헬스&amp;PT&amp;필라테스&amp;스피닝 사상점</t>
+          <t>피에스짐 주례점 헬스 PT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>healthstar02@naver.com</t>
+          <t>ps_gym_4@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1448-0905</t>
+          <t>0507-1445-0954</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로81번길 30 8~10층 뉴핏 사상점</t>
+          <t>부산광역시 사상구 백양대로357번길 33 1층 피에스짐 주례점</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/newfit_sasang</t>
+          <t>https://blog.naver.com/ps_gym_4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6621,13 +6621,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>357</v>
+        <v>619</v>
       </c>
       <c r="Q66" t="n">
-        <v>235</v>
+        <v>759</v>
       </c>
       <c r="R66" t="n">
-        <v>592</v>
+        <v>1378</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6636,51 +6636,51 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>603428544</t>
+          <t>1182425609</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/603428544</t>
+          <t>https://m.place.naver.com/place/1182425609</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>합기도</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>건아합기도</t>
+          <t>올데이 그룹PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>dagymfit@naver.com</t>
+          <t>yolo__j@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1487-2777</t>
+          <t>0507-1393-9684</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 508 2층</t>
+          <t>부산광역시 부산진구 가야대로 472 보문빌딩 4층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dagymfit</t>
+          <t>https://www.instagram.com/allday__gg</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
       <c r="R67" t="n">
-        <v>1</v>
+        <v>438</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,17 +6730,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>13208389</t>
+          <t>1958976432</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13208389</t>
+          <t>https://m.place.naver.com/place/1958976432</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6752,29 +6752,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>알통클럽 휘트니스</t>
+          <t>팰리스피트니스 헬스&amp;PT 1호점 모라</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>daeilband007@naver.com</t>
+          <t>palace7979@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>051-317-2999</t>
+          <t>0507-1312-5736</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 낙동대로 751 동일메가타워 7층 알통클럽휘트니스</t>
+          <t>부산광역시 사상구 백양대로 893 B1 (제일약국 / 참좋은 내과 / 뚜레쥬르 건물)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/daeilband007</t>
+          <t>https://www.instagram.com/palacefitness_official/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -6809,13 +6809,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="Q68" t="n">
-        <v>296</v>
+        <v>509</v>
       </c>
       <c r="R68" t="n">
-        <v>444</v>
+        <v>783</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6824,51 +6824,51 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>35769362</t>
+          <t>1942470035</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35769362</t>
+          <t>https://m.place.naver.com/place/1942470035</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>필라걸 사상점</t>
+          <t>동아기능성운동트레이닝센터</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>pilasasang@naver.com</t>
+          <t>dfet0226@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>051-313-3232</t>
+          <t>0507-1494-7910</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로81번길 30 8,9층 필라걸</t>
+          <t>부산광역시 사하구 낙동대로550번길 37 예술체육대학1관 106호</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pilasasang</t>
+          <t>https://blog.naver.com/dfet0226</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6903,13 +6903,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="R69" t="n">
-        <v>55</v>
+        <v>462</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6918,17 +6918,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1538621837</t>
+          <t>1619665911</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1538621837</t>
+          <t>https://m.place.naver.com/place/1619665911</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6940,29 +6940,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>이루짐 PT/헬스 개금점</t>
+          <t>더인핏PT&amp;헬스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>hjoo4030@naver.com</t>
+          <t>the-infit@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1312-4287</t>
+          <t>0507-1340-3051</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 가야대로 456 금성빌딩 12층</t>
+          <t>부산광역시 사상구 사상로 201 애플아울렛 별관 B동 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hjoo4030</t>
+          <t>https://blog.naver.com/the-infit</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6993,17 +6993,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>246</v>
+        <v>935</v>
       </c>
       <c r="Q70" t="n">
-        <v>232</v>
+        <v>599</v>
       </c>
       <c r="R70" t="n">
-        <v>478</v>
+        <v>1534</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7012,51 +7012,51 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1512480674</t>
+          <t>1307555029</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1512480674</t>
+          <t>https://m.place.naver.com/place/1307555029</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>메이트 Mate PT &amp; 헬스</t>
+          <t>트랜스바디짐 학장점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>matept@naver.com</t>
+          <t>transbody02@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1483-1032</t>
+          <t>0507-1364-9625</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 북구 덕천로247번길 1 2층</t>
+          <t>부산광역시 사상구 학감대로123번길 68 AK 빌딩 삼정그린코아 맞은편</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/matept</t>
+          <t>https://youtube.com/@트랜스바디짐학장점</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>377</v>
       </c>
       <c r="R71" t="n">
-        <v>56</v>
+        <v>462</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7106,17 +7106,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1118741658</t>
+          <t>37335417</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1118741658</t>
+          <t>https://m.place.naver.com/place/37335417</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7128,29 +7128,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>엘리먼트 휘트니스</t>
+          <t>에이치포스포츠</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>kycbyc@naver.com</t>
+          <t>atbud008@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>051-304-2255</t>
+          <t>051-715-0705</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 987 스파캐슬 7층 엘리먼트 휘트니스</t>
+          <t>부산광역시 사상구 백양대로 945 3층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/element_fitness987</t>
+          <t>https://blog.naver.com/atbud008</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7181,17 +7181,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="Q72" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="R72" t="n">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7200,66 +7200,66 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>11878707</t>
+          <t>465072208</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11878707</t>
+          <t>https://m.place.naver.com/place/465072208</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;PT 하단점</t>
+          <t>개금 리부트핏 PT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>404fitnesshadan@naver.com</t>
+          <t>reboot_fit@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1395-4026</t>
+          <t>0507-1357-9397</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 487 4층</t>
+          <t>부산광역시 부산진구 냉정로 214 . 2층(개금동)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/404_fitness_hadan/</t>
+          <t>https://m.blog.naver.com/reboot_fit</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7270,7 +7270,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>403</v>
+        <v>46</v>
       </c>
       <c r="Q73" t="n">
-        <v>278</v>
+        <v>149</v>
       </c>
       <c r="R73" t="n">
-        <v>681</v>
+        <v>195</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7294,51 +7294,51 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1669341529</t>
+          <t>1668633780</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1669341529</t>
+          <t>https://m.place.naver.com/place/1668633780</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;pt 사상점</t>
+          <t>뉴핏 헬스&amp;PT&amp;필라테스&amp;스피닝 사상점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>404sasang_@naver.com</t>
+          <t>healthstar02@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1309-4044</t>
+          <t>0507-1448-0905</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 광장로 84 하이앤드 4, 5층</t>
+          <t>부산광역시 사상구 광장로81번길 30 8~10층 뉴핏 사상점</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/404sasang_</t>
+          <t>https://www.instagram.com/newfit_sasang</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7373,13 +7373,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>581</v>
+        <v>357</v>
       </c>
       <c r="Q74" t="n">
-        <v>672</v>
+        <v>242</v>
       </c>
       <c r="R74" t="n">
-        <v>1253</v>
+        <v>599</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7388,17 +7388,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1720813988</t>
+          <t>603428544</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720813988</t>
+          <t>https://m.place.naver.com/place/603428544</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7410,34 +7410,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>핏튜브짐 &amp; 필라테스</t>
+          <t>뉴인핏 PT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>boong_see@naver.com</t>
+          <t>in-fit@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1465-5152</t>
+          <t>0507-1414-4020</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 하신번영로 417 2층</t>
+          <t>부산광역시 사상구 사상로 182 청호빌딩 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/749373</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7463,17 +7463,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="Q75" t="n">
-        <v>29</v>
+        <v>2000</v>
       </c>
       <c r="R75" t="n">
-        <v>37</v>
+        <v>2267</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7482,51 +7482,51 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1226166767</t>
+          <t>38643118</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226166767</t>
+          <t>https://m.place.naver.com/place/38643118</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>트랜스바디짐 주례점</t>
+          <t>오성피트니스 대신점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>pysook53@naver.com</t>
+          <t>momjjang_@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1407-6891</t>
+          <t>0507-1439-5553</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 사상구 백양대로 372-16 주례반도보라상가 4층</t>
+          <t>부산광역시 서구 보수대로 198-1 1, 2층 오성피트니스</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pysook53</t>
+          <t>https://blog.naver.com/momjjang_</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="Q76" t="n">
-        <v>246</v>
+        <v>487</v>
       </c>
       <c r="R76" t="n">
-        <v>257</v>
+        <v>630</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7576,17 +7576,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>33085242</t>
+          <t>1944190273</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33085242</t>
+          <t>https://m.place.naver.com/place/1944190273</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
